--- a/reviews/REVIEWED_StateRepHong_20210107_20220902_20260806_autoPush.xlsx
+++ b/reviews/REVIEWED_StateRepHong_20210107_20220902_20260806_autoPush.xlsx
@@ -19623,7 +19623,7 @@
         <v>0</v>
       </c>
       <c r="J441" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K441" t="inlineStr"/>
     </row>
